--- a/master-slave/outputs/exp1-full/runs.xlsx
+++ b/master-slave/outputs/exp1-full/runs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1121"/>
+  <dimension ref="A1:K1142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44153,6 +44153,699 @@
         <v>19796063983</v>
       </c>
     </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>1000.10.1</t>
+        </is>
+      </c>
+      <c r="B1122" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1122" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>1773.817056086561</v>
+      </c>
+      <c r="H1122" t="n">
+        <v>1778.507423936863</v>
+      </c>
+      <c r="J1122" t="n">
+        <v>58539266407</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>1000.10.1</t>
+        </is>
+      </c>
+      <c r="B1123" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1123" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>1773.817056086561</v>
+      </c>
+      <c r="H1123" t="n">
+        <v>1771.763056955113</v>
+      </c>
+      <c r="J1123" t="n">
+        <v>58184281775</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>1000.10.1</t>
+        </is>
+      </c>
+      <c r="B1124" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1124" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>1773.817056086561</v>
+      </c>
+      <c r="H1124" t="n">
+        <v>1763.5844050743</v>
+      </c>
+      <c r="J1124" t="n">
+        <v>58356516054</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>1000.10.2</t>
+        </is>
+      </c>
+      <c r="B1125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1125" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>1761.739356115498</v>
+      </c>
+      <c r="H1125" t="n">
+        <v>1748.663684856989</v>
+      </c>
+      <c r="J1125" t="n">
+        <v>58812269481</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>1000.10.2</t>
+        </is>
+      </c>
+      <c r="B1126" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1126" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>1761.739356115498</v>
+      </c>
+      <c r="H1126" t="n">
+        <v>1753.0778443804</v>
+      </c>
+      <c r="J1126" t="n">
+        <v>58793302310</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>1000.10.2</t>
+        </is>
+      </c>
+      <c r="B1127" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1127" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>1761.739356115498</v>
+      </c>
+      <c r="H1127" t="n">
+        <v>1733.720824201108</v>
+      </c>
+      <c r="J1127" t="n">
+        <v>58755870420</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>1000.10.3</t>
+        </is>
+      </c>
+      <c r="B1128" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1128" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>1748.302363736126</v>
+      </c>
+      <c r="H1128" t="n">
+        <v>1764.908007473116</v>
+      </c>
+      <c r="J1128" t="n">
+        <v>58893253402</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>1000.10.3</t>
+        </is>
+      </c>
+      <c r="B1129" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1129" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>1748.302363736126</v>
+      </c>
+      <c r="H1129" t="n">
+        <v>1745.232279618789</v>
+      </c>
+      <c r="J1129" t="n">
+        <v>59297447103</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>1000.10.3</t>
+        </is>
+      </c>
+      <c r="B1130" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1130" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>1748.302363736126</v>
+      </c>
+      <c r="H1130" t="n">
+        <v>1753.412563400108</v>
+      </c>
+      <c r="J1130" t="n">
+        <v>59138365297</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>1000.10.4</t>
+        </is>
+      </c>
+      <c r="B1131" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1131" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>1745.548800328407</v>
+      </c>
+      <c r="H1131" t="n">
+        <v>1724.519140458432</v>
+      </c>
+      <c r="J1131" t="n">
+        <v>59718078278</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>1000.10.4</t>
+        </is>
+      </c>
+      <c r="B1132" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1132" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>1745.548800328407</v>
+      </c>
+      <c r="H1132" t="n">
+        <v>1727.349755495702</v>
+      </c>
+      <c r="J1132" t="n">
+        <v>59700888210</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>1000.10.4</t>
+        </is>
+      </c>
+      <c r="B1133" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1133" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>1745.548800328407</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>1716.732256778813</v>
+      </c>
+      <c r="J1133" t="n">
+        <v>59511032983</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>1000.20.1</t>
+        </is>
+      </c>
+      <c r="B1134" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1134" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>3708.541021396037</v>
+      </c>
+      <c r="H1134" t="n">
+        <v>3711.484141374198</v>
+      </c>
+      <c r="J1134" t="n">
+        <v>54539220721</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>1000.20.1</t>
+        </is>
+      </c>
+      <c r="B1135" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1135" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>3708.541021396037</v>
+      </c>
+      <c r="H1135" t="n">
+        <v>3717.075646092836</v>
+      </c>
+      <c r="J1135" t="n">
+        <v>54746244345</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>1000.20.1</t>
+        </is>
+      </c>
+      <c r="B1136" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1136" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>3708.541021396037</v>
+      </c>
+      <c r="H1136" t="n">
+        <v>3709.542619220546</v>
+      </c>
+      <c r="J1136" t="n">
+        <v>54542720537</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>1000.20.2</t>
+        </is>
+      </c>
+      <c r="B1137" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1137" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>3768.103517429845</v>
+      </c>
+      <c r="H1137" t="n">
+        <v>3718.334914449701</v>
+      </c>
+      <c r="J1137" t="n">
+        <v>54522257604</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>1000.20.2</t>
+        </is>
+      </c>
+      <c r="B1138" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1138" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>3768.103517429845</v>
+      </c>
+      <c r="H1138" t="n">
+        <v>3712.59434092089</v>
+      </c>
+      <c r="J1138" t="n">
+        <v>54713477727</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>1000.20.2</t>
+        </is>
+      </c>
+      <c r="B1139" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1139" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1139" t="n">
+        <v>3768.103517429845</v>
+      </c>
+      <c r="H1139" t="n">
+        <v>3730.776752188581</v>
+      </c>
+      <c r="J1139" t="n">
+        <v>54778015958</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>1000.20.3</t>
+        </is>
+      </c>
+      <c r="B1140" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1140" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1140" t="n">
+        <v>3734.724211492563</v>
+      </c>
+      <c r="H1140" t="n">
+        <v>3675.718557688236</v>
+      </c>
+      <c r="J1140" t="n">
+        <v>55234934660</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>1000.20.3</t>
+        </is>
+      </c>
+      <c r="B1141" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1141" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1141" t="n">
+        <v>3734.724211492563</v>
+      </c>
+      <c r="H1141" t="n">
+        <v>3671.040088594132</v>
+      </c>
+      <c r="J1141" t="n">
+        <v>55008199465</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>1000.20.3</t>
+        </is>
+      </c>
+      <c r="B1142" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1142" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1142" t="n">
+        <v>3734.724211492563</v>
+      </c>
+      <c r="H1142" t="n">
+        <v>3679.658407988477</v>
+      </c>
+      <c r="J1142" t="n">
+        <v>54859740947</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master-slave/outputs/exp1-full/runs.xlsx
+++ b/master-slave/outputs/exp1-full/runs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1142"/>
+  <dimension ref="A1:K1169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44846,6 +44846,897 @@
         <v>54859740947</v>
       </c>
     </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>1000.20.4</t>
+        </is>
+      </c>
+      <c r="B1143" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1143" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1143" t="n">
+        <v>3750.289861862383</v>
+      </c>
+      <c r="H1143" t="n">
+        <v>3676.25923851024</v>
+      </c>
+      <c r="J1143" t="n">
+        <v>55598291229</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>1000.20.4</t>
+        </is>
+      </c>
+      <c r="B1144" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1144" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1144" t="n">
+        <v>3750.289861862383</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>3662.58440372612</v>
+      </c>
+      <c r="J1144" t="n">
+        <v>55666781684</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>1000.20.4</t>
+        </is>
+      </c>
+      <c r="B1145" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1145" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1145" t="n">
+        <v>3750.289861862383</v>
+      </c>
+      <c r="H1145" t="n">
+        <v>3640.786747235285</v>
+      </c>
+      <c r="J1145" t="n">
+        <v>55705986427</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>1000.30.1</t>
+        </is>
+      </c>
+      <c r="B1146" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1146" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1146" t="n">
+        <v>7979.543044930953</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>7909.942853594655</v>
+      </c>
+      <c r="J1146" t="n">
+        <v>75322972139</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>1000.30.1</t>
+        </is>
+      </c>
+      <c r="B1147" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1147" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1147" t="n">
+        <v>7979.543044930953</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>7933.369653078021</v>
+      </c>
+      <c r="J1147" t="n">
+        <v>75779392870</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>1000.30.1</t>
+        </is>
+      </c>
+      <c r="B1148" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1148" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1148" t="n">
+        <v>7979.543044930953</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>7938.674740845327</v>
+      </c>
+      <c r="J1148" t="n">
+        <v>75826655517</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>1000.30.2</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1149" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1149" t="n">
+        <v>7973.009423005142</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>7955.478963396214</v>
+      </c>
+      <c r="J1149" t="n">
+        <v>75463252430</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>1000.30.2</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1150" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1150" t="n">
+        <v>7973.009423005142</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>7985.667796737807</v>
+      </c>
+      <c r="J1150" t="n">
+        <v>75499709671</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>1000.30.2</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1151" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1151" t="n">
+        <v>7973.009423005142</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>7971.863557246797</v>
+      </c>
+      <c r="J1151" t="n">
+        <v>75291910014</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>1000.30.3</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1152" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1152" t="n">
+        <v>7977.814850915422</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>7912.800374705674</v>
+      </c>
+      <c r="J1152" t="n">
+        <v>75526679782</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>1000.30.3</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1153" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1153" t="n">
+        <v>7977.814850915422</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>7920.286934325561</v>
+      </c>
+      <c r="J1153" t="n">
+        <v>75239934410</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>1000.30.3</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1154" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>7977.814850915422</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>7913.559085252405</v>
+      </c>
+      <c r="J1154" t="n">
+        <v>75154106633</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>1000.30.4</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1155" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>7964.046250435393</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>7954.622756722229</v>
+      </c>
+      <c r="J1155" t="n">
+        <v>76298686901</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>1000.30.4</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1156" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1156" t="n">
+        <v>7964.046250435393</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>7944.878378597256</v>
+      </c>
+      <c r="J1156" t="n">
+        <v>76143958723</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>1000.30.4</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1157" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>7964.046250435393</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>7908.149940826446</v>
+      </c>
+      <c r="J1157" t="n">
+        <v>76310818841</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>1000.40.1</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1158" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>14005.02994874948</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>13804.65911026816</v>
+      </c>
+      <c r="J1158" t="n">
+        <v>85252367167</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>1000.40.1</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1159" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1159" t="n">
+        <v>14005.02994874948</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>13703.5761313689</v>
+      </c>
+      <c r="J1159" t="n">
+        <v>85000059396</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>1000.40.1</t>
+        </is>
+      </c>
+      <c r="B1160" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1160" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>14005.02994874948</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>13829.70485039924</v>
+      </c>
+      <c r="J1160" t="n">
+        <v>84913861591</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>1000.40.2</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1161" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>14118.04105210099</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>13953.57733794516</v>
+      </c>
+      <c r="J1161" t="n">
+        <v>84476830074</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>1000.40.2</t>
+        </is>
+      </c>
+      <c r="B1162" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1162" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>14118.04105210099</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>13879.86269944144</v>
+      </c>
+      <c r="J1162" t="n">
+        <v>84567750703</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>1000.40.2</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1163" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>14118.04105210099</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>13960.02681644472</v>
+      </c>
+      <c r="J1163" t="n">
+        <v>84895471386</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>1000.40.3</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1164" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>14052.70747046845</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>13928.43424030587</v>
+      </c>
+      <c r="J1164" t="n">
+        <v>84955360440</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>1000.40.3</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1165" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>14052.70747046845</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>14025.13225262927</v>
+      </c>
+      <c r="J1165" t="n">
+        <v>84845024911</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>1000.40.3</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1166" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1166" t="n">
+        <v>14052.70747046845</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>13988.34944155203</v>
+      </c>
+      <c r="J1166" t="n">
+        <v>85041302241</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>1000.40.4</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1167" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1167" t="n">
+        <v>14047.58679159633</v>
+      </c>
+      <c r="H1167" t="n">
+        <v>13855.13481452877</v>
+      </c>
+      <c r="J1167" t="n">
+        <v>84108180671</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>1000.40.4</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1168" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>14047.58679159633</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>13808.05311567009</v>
+      </c>
+      <c r="J1168" t="n">
+        <v>83932164076</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>1000.40.4</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1169" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1169" t="n">
+        <v>14047.58679159633</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>13788.06577326823</v>
+      </c>
+      <c r="J1169" t="n">
+        <v>84099856887</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master-slave/outputs/exp1-full/runs.xlsx
+++ b/master-slave/outputs/exp1-full/runs.xlsx
@@ -44182,9 +44182,15 @@
       <c r="H1122" t="n">
         <v>1778.507423936863</v>
       </c>
+      <c r="I1122" t="n">
+        <v>1764.272173140725</v>
+      </c>
       <c r="J1122" t="n">
         <v>58539266407</v>
       </c>
+      <c r="K1122" t="n">
+        <v>60948511285</v>
+      </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
@@ -44215,9 +44221,15 @@
       <c r="H1123" t="n">
         <v>1771.763056955113</v>
       </c>
+      <c r="I1123" t="n">
+        <v>1779.000878365724</v>
+      </c>
       <c r="J1123" t="n">
         <v>58184281775</v>
       </c>
+      <c r="K1123" t="n">
+        <v>60471533318</v>
+      </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
@@ -44248,9 +44260,15 @@
       <c r="H1124" t="n">
         <v>1763.5844050743</v>
       </c>
+      <c r="I1124" t="n">
+        <v>1771.506857743069</v>
+      </c>
       <c r="J1124" t="n">
         <v>58356516054</v>
       </c>
+      <c r="K1124" t="n">
+        <v>60447161693</v>
+      </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
@@ -44281,9 +44299,15 @@
       <c r="H1125" t="n">
         <v>1748.663684856989</v>
       </c>
+      <c r="I1125" t="n">
+        <v>1742.937265530643</v>
+      </c>
       <c r="J1125" t="n">
         <v>58812269481</v>
       </c>
+      <c r="K1125" t="n">
+        <v>61315522970</v>
+      </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
@@ -44314,9 +44338,15 @@
       <c r="H1126" t="n">
         <v>1753.0778443804</v>
       </c>
+      <c r="I1126" t="n">
+        <v>1743.318234245733</v>
+      </c>
       <c r="J1126" t="n">
         <v>58793302310</v>
       </c>
+      <c r="K1126" t="n">
+        <v>61145794679</v>
+      </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
@@ -44347,9 +44377,15 @@
       <c r="H1127" t="n">
         <v>1733.720824201108</v>
       </c>
+      <c r="I1127" t="n">
+        <v>1740.796072994495</v>
+      </c>
       <c r="J1127" t="n">
         <v>58755870420</v>
       </c>
+      <c r="K1127" t="n">
+        <v>61540538472</v>
+      </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
@@ -44380,9 +44416,15 @@
       <c r="H1128" t="n">
         <v>1764.908007473116</v>
       </c>
+      <c r="I1128" t="n">
+        <v>1760.654491641879</v>
+      </c>
       <c r="J1128" t="n">
         <v>58893253402</v>
       </c>
+      <c r="K1128" t="n">
+        <v>61164450752</v>
+      </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
@@ -44413,9 +44455,15 @@
       <c r="H1129" t="n">
         <v>1745.232279618789</v>
       </c>
+      <c r="I1129" t="n">
+        <v>1749.202199750996</v>
+      </c>
       <c r="J1129" t="n">
         <v>59297447103</v>
       </c>
+      <c r="K1129" t="n">
+        <v>61614359995</v>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
@@ -44446,9 +44494,15 @@
       <c r="H1130" t="n">
         <v>1753.412563400108</v>
       </c>
+      <c r="I1130" t="n">
+        <v>1746.964360199898</v>
+      </c>
       <c r="J1130" t="n">
         <v>59138365297</v>
       </c>
+      <c r="K1130" t="n">
+        <v>61283413634</v>
+      </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
@@ -44479,9 +44533,15 @@
       <c r="H1131" t="n">
         <v>1724.519140458432</v>
       </c>
+      <c r="I1131" t="n">
+        <v>1730.539238991366</v>
+      </c>
       <c r="J1131" t="n">
         <v>59718078278</v>
       </c>
+      <c r="K1131" t="n">
+        <v>62112379253</v>
+      </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
@@ -44512,9 +44572,15 @@
       <c r="H1132" t="n">
         <v>1727.349755495702</v>
       </c>
+      <c r="I1132" t="n">
+        <v>1728.751156453611</v>
+      </c>
       <c r="J1132" t="n">
         <v>59700888210</v>
       </c>
+      <c r="K1132" t="n">
+        <v>61935437391</v>
+      </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
@@ -44545,9 +44611,15 @@
       <c r="H1133" t="n">
         <v>1716.732256778813</v>
       </c>
+      <c r="I1133" t="n">
+        <v>1720.205219492753</v>
+      </c>
       <c r="J1133" t="n">
         <v>59511032983</v>
       </c>
+      <c r="K1133" t="n">
+        <v>62016875497</v>
+      </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
@@ -44578,9 +44650,15 @@
       <c r="H1134" t="n">
         <v>3711.484141374198</v>
       </c>
+      <c r="I1134" t="n">
+        <v>3709.684088929843</v>
+      </c>
       <c r="J1134" t="n">
         <v>54539220721</v>
       </c>
+      <c r="K1134" t="n">
+        <v>57058097271</v>
+      </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
@@ -44611,9 +44689,15 @@
       <c r="H1135" t="n">
         <v>3717.075646092836</v>
       </c>
+      <c r="I1135" t="n">
+        <v>3712.684249728848</v>
+      </c>
       <c r="J1135" t="n">
         <v>54746244345</v>
       </c>
+      <c r="K1135" t="n">
+        <v>57502335211</v>
+      </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
@@ -44644,9 +44728,15 @@
       <c r="H1136" t="n">
         <v>3709.542619220546</v>
       </c>
+      <c r="I1136" t="n">
+        <v>3710.003790441718</v>
+      </c>
       <c r="J1136" t="n">
         <v>54542720537</v>
       </c>
+      <c r="K1136" t="n">
+        <v>57084344927</v>
+      </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
@@ -44677,9 +44767,15 @@
       <c r="H1137" t="n">
         <v>3718.334914449701</v>
       </c>
+      <c r="I1137" t="n">
+        <v>3707.205779416522</v>
+      </c>
       <c r="J1137" t="n">
         <v>54522257604</v>
       </c>
+      <c r="K1137" t="n">
+        <v>56748923914</v>
+      </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
@@ -44710,9 +44806,15 @@
       <c r="H1138" t="n">
         <v>3712.59434092089</v>
       </c>
+      <c r="I1138" t="n">
+        <v>3688.571250633831</v>
+      </c>
       <c r="J1138" t="n">
         <v>54713477727</v>
       </c>
+      <c r="K1138" t="n">
+        <v>57558889306</v>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
@@ -44743,9 +44845,15 @@
       <c r="H1139" t="n">
         <v>3730.776752188581</v>
       </c>
+      <c r="I1139" t="n">
+        <v>3725.00272664874</v>
+      </c>
       <c r="J1139" t="n">
         <v>54778015958</v>
       </c>
+      <c r="K1139" t="n">
+        <v>57374818287</v>
+      </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
@@ -44776,9 +44884,15 @@
       <c r="H1140" t="n">
         <v>3675.718557688236</v>
       </c>
+      <c r="I1140" t="n">
+        <v>3679.378142308556</v>
+      </c>
       <c r="J1140" t="n">
         <v>55234934660</v>
       </c>
+      <c r="K1140" t="n">
+        <v>57888578439</v>
+      </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
@@ -44809,9 +44923,15 @@
       <c r="H1141" t="n">
         <v>3671.040088594132</v>
       </c>
+      <c r="I1141" t="n">
+        <v>3661.716562358774</v>
+      </c>
       <c r="J1141" t="n">
         <v>55008199465</v>
       </c>
+      <c r="K1141" t="n">
+        <v>58027715698</v>
+      </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
@@ -44842,9 +44962,15 @@
       <c r="H1142" t="n">
         <v>3679.658407988477</v>
       </c>
+      <c r="I1142" t="n">
+        <v>3666.047778478794</v>
+      </c>
       <c r="J1142" t="n">
         <v>54859740947</v>
       </c>
+      <c r="K1142" t="n">
+        <v>57560856429</v>
+      </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
@@ -44875,9 +45001,15 @@
       <c r="H1143" t="n">
         <v>3676.25923851024</v>
       </c>
+      <c r="I1143" t="n">
+        <v>3670.733398781877</v>
+      </c>
       <c r="J1143" t="n">
         <v>55598291229</v>
       </c>
+      <c r="K1143" t="n">
+        <v>58759408779</v>
+      </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
@@ -44908,9 +45040,15 @@
       <c r="H1144" t="n">
         <v>3662.58440372612</v>
       </c>
+      <c r="I1144" t="n">
+        <v>3636.649673462108</v>
+      </c>
       <c r="J1144" t="n">
         <v>55666781684</v>
       </c>
+      <c r="K1144" t="n">
+        <v>58678113114</v>
+      </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
@@ -44941,9 +45079,15 @@
       <c r="H1145" t="n">
         <v>3640.786747235285</v>
       </c>
+      <c r="I1145" t="n">
+        <v>3626.928613219296</v>
+      </c>
       <c r="J1145" t="n">
         <v>55705986427</v>
       </c>
+      <c r="K1145" t="n">
+        <v>58360786268</v>
+      </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
@@ -44974,9 +45118,15 @@
       <c r="H1146" t="n">
         <v>7909.942853594655</v>
       </c>
+      <c r="I1146" t="n">
+        <v>7903.870424714833</v>
+      </c>
       <c r="J1146" t="n">
         <v>75322972139</v>
       </c>
+      <c r="K1146" t="n">
+        <v>80290385520</v>
+      </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
@@ -45007,9 +45157,15 @@
       <c r="H1147" t="n">
         <v>7933.369653078021</v>
       </c>
+      <c r="I1147" t="n">
+        <v>7887.053929253325</v>
+      </c>
       <c r="J1147" t="n">
         <v>75779392870</v>
       </c>
+      <c r="K1147" t="n">
+        <v>80350357454</v>
+      </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
@@ -45040,9 +45196,15 @@
       <c r="H1148" t="n">
         <v>7938.674740845327</v>
       </c>
+      <c r="I1148" t="n">
+        <v>7907.193593195034</v>
+      </c>
       <c r="J1148" t="n">
         <v>75826655517</v>
       </c>
+      <c r="K1148" t="n">
+        <v>80336749536</v>
+      </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
@@ -45073,9 +45235,15 @@
       <c r="H1149" t="n">
         <v>7955.478963396214</v>
       </c>
+      <c r="I1149" t="n">
+        <v>7944.300020434308</v>
+      </c>
       <c r="J1149" t="n">
         <v>75463252430</v>
       </c>
+      <c r="K1149" t="n">
+        <v>79665719147</v>
+      </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
@@ -45106,8 +45274,14 @@
       <c r="H1150" t="n">
         <v>7985.667796737807</v>
       </c>
+      <c r="I1150" t="n">
+        <v>7950.033926181859</v>
+      </c>
       <c r="J1150" t="n">
         <v>75499709671</v>
+      </c>
+      <c r="K1150" t="n">
+        <v>79559486593</v>
       </c>
     </row>
     <row r="1151">

--- a/master-slave/outputs/exp1-full/runs.xlsx
+++ b/master-slave/outputs/exp1-full/runs.xlsx
@@ -45313,9 +45313,15 @@
       <c r="H1151" t="n">
         <v>7971.863557246797</v>
       </c>
+      <c r="I1151" t="n">
+        <v>7945.713457379617</v>
+      </c>
       <c r="J1151" t="n">
         <v>75291910014</v>
       </c>
+      <c r="K1151" t="n">
+        <v>79646776106</v>
+      </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
@@ -45346,9 +45352,15 @@
       <c r="H1152" t="n">
         <v>7912.800374705674</v>
       </c>
+      <c r="I1152" t="n">
+        <v>7920.722535902631</v>
+      </c>
       <c r="J1152" t="n">
         <v>75526679782</v>
       </c>
+      <c r="K1152" t="n">
+        <v>79864223403</v>
+      </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
@@ -45379,9 +45391,15 @@
       <c r="H1153" t="n">
         <v>7920.286934325561</v>
       </c>
+      <c r="I1153" t="n">
+        <v>7876.350396623391</v>
+      </c>
       <c r="J1153" t="n">
         <v>75239934410</v>
       </c>
+      <c r="K1153" t="n">
+        <v>79854507057</v>
+      </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
@@ -45412,9 +45430,15 @@
       <c r="H1154" t="n">
         <v>7913.559085252405</v>
       </c>
+      <c r="I1154" t="n">
+        <v>7860.33109598247</v>
+      </c>
       <c r="J1154" t="n">
         <v>75154106633</v>
       </c>
+      <c r="K1154" t="n">
+        <v>79559590331</v>
+      </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
@@ -45445,9 +45469,15 @@
       <c r="H1155" t="n">
         <v>7954.622756722229</v>
       </c>
+      <c r="I1155" t="n">
+        <v>7937.350316798198</v>
+      </c>
       <c r="J1155" t="n">
         <v>76298686901</v>
       </c>
+      <c r="K1155" t="n">
+        <v>80345994552</v>
+      </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
@@ -45478,9 +45508,15 @@
       <c r="H1156" t="n">
         <v>7944.878378597256</v>
       </c>
+      <c r="I1156" t="n">
+        <v>7945.437917149456</v>
+      </c>
       <c r="J1156" t="n">
         <v>76143958723</v>
       </c>
+      <c r="K1156" t="n">
+        <v>80072300346</v>
+      </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
@@ -45511,9 +45547,15 @@
       <c r="H1157" t="n">
         <v>7908.149940826446</v>
       </c>
+      <c r="I1157" t="n">
+        <v>7924.585067946708</v>
+      </c>
       <c r="J1157" t="n">
         <v>76310818841</v>
       </c>
+      <c r="K1157" t="n">
+        <v>80329220533</v>
+      </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -45544,9 +45586,15 @@
       <c r="H1158" t="n">
         <v>13804.65911026816</v>
       </c>
+      <c r="I1158" t="n">
+        <v>13727.06070999957</v>
+      </c>
       <c r="J1158" t="n">
         <v>85252367167</v>
       </c>
+      <c r="K1158" t="n">
+        <v>87948448001</v>
+      </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
@@ -45577,9 +45625,15 @@
       <c r="H1159" t="n">
         <v>13703.5761313689</v>
       </c>
+      <c r="I1159" t="n">
+        <v>13678.77539809002</v>
+      </c>
       <c r="J1159" t="n">
         <v>85000059396</v>
       </c>
+      <c r="K1159" t="n">
+        <v>88387691033</v>
+      </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
@@ -45610,9 +45664,15 @@
       <c r="H1160" t="n">
         <v>13829.70485039924</v>
       </c>
+      <c r="I1160" t="n">
+        <v>13707.46434839891</v>
+      </c>
       <c r="J1160" t="n">
         <v>84913861591</v>
       </c>
+      <c r="K1160" t="n">
+        <v>88130654686</v>
+      </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
@@ -45643,9 +45703,15 @@
       <c r="H1161" t="n">
         <v>13953.57733794516</v>
       </c>
+      <c r="I1161" t="n">
+        <v>13931.39017551439</v>
+      </c>
       <c r="J1161" t="n">
         <v>84476830074</v>
       </c>
+      <c r="K1161" t="n">
+        <v>88463191445</v>
+      </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -45676,9 +45742,15 @@
       <c r="H1162" t="n">
         <v>13879.86269944144</v>
       </c>
+      <c r="I1162" t="n">
+        <v>13850.72930858321</v>
+      </c>
       <c r="J1162" t="n">
         <v>84567750703</v>
       </c>
+      <c r="K1162" t="n">
+        <v>88374159109</v>
+      </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
@@ -45709,9 +45781,15 @@
       <c r="H1163" t="n">
         <v>13960.02681644472</v>
       </c>
+      <c r="I1163" t="n">
+        <v>13917.82365179558</v>
+      </c>
       <c r="J1163" t="n">
         <v>84895471386</v>
       </c>
+      <c r="K1163" t="n">
+        <v>88267450156</v>
+      </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
@@ -45742,9 +45820,15 @@
       <c r="H1164" t="n">
         <v>13928.43424030587</v>
       </c>
+      <c r="I1164" t="n">
+        <v>13866.49181471369</v>
+      </c>
       <c r="J1164" t="n">
         <v>84955360440</v>
       </c>
+      <c r="K1164" t="n">
+        <v>88491758334</v>
+      </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
@@ -45775,9 +45859,15 @@
       <c r="H1165" t="n">
         <v>14025.13225262927</v>
       </c>
+      <c r="I1165" t="n">
+        <v>13992.15523571734</v>
+      </c>
       <c r="J1165" t="n">
         <v>84845024911</v>
       </c>
+      <c r="K1165" t="n">
+        <v>88258794676</v>
+      </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
@@ -45808,9 +45898,15 @@
       <c r="H1166" t="n">
         <v>13988.34944155203</v>
       </c>
+      <c r="I1166" t="n">
+        <v>13922.58586497711</v>
+      </c>
       <c r="J1166" t="n">
         <v>85041302241</v>
       </c>
+      <c r="K1166" t="n">
+        <v>88291746606</v>
+      </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
@@ -45841,9 +45937,15 @@
       <c r="H1167" t="n">
         <v>13855.13481452877</v>
       </c>
+      <c r="I1167" t="n">
+        <v>13769.51168139956</v>
+      </c>
       <c r="J1167" t="n">
         <v>84108180671</v>
       </c>
+      <c r="K1167" t="n">
+        <v>88169613935</v>
+      </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
@@ -45874,9 +45976,15 @@
       <c r="H1168" t="n">
         <v>13808.05311567009</v>
       </c>
+      <c r="I1168" t="n">
+        <v>13792.0484138216</v>
+      </c>
       <c r="J1168" t="n">
         <v>83932164076</v>
       </c>
+      <c r="K1168" t="n">
+        <v>87849710144</v>
+      </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
@@ -45907,8 +46015,14 @@
       <c r="H1169" t="n">
         <v>13788.06577326823</v>
       </c>
+      <c r="I1169" t="n">
+        <v>13833.52844773018</v>
+      </c>
       <c r="J1169" t="n">
         <v>84099856887</v>
+      </c>
+      <c r="K1169" t="n">
+        <v>88168171393</v>
       </c>
     </row>
   </sheetData>

--- a/master-slave/outputs/exp1-full/runs.xlsx
+++ b/master-slave/outputs/exp1-full/runs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1169"/>
+  <dimension ref="A1:K1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44273,7 +44273,7 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>1000.10.2</t>
+          <t>1000.10.1</t>
         </is>
       </c>
       <c r="B1125" t="n">
@@ -44288,31 +44288,25 @@
         <v>4500</v>
       </c>
       <c r="E1125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1125" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G1125" t="n">
-        <v>1761.739356115498</v>
-      </c>
-      <c r="H1125" t="n">
-        <v>1748.663684856989</v>
+        <v>1773.817056086561</v>
       </c>
       <c r="I1125" t="n">
-        <v>1742.937265530643</v>
-      </c>
-      <c r="J1125" t="n">
-        <v>58812269481</v>
+        <v>1754.17297722392</v>
       </c>
       <c r="K1125" t="n">
-        <v>61315522970</v>
+        <v>60823425788</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>1000.10.2</t>
+          <t>1000.10.1</t>
         </is>
       </c>
       <c r="B1126" t="n">
@@ -44327,25 +44321,19 @@
         <v>4500</v>
       </c>
       <c r="E1126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1126" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G1126" t="n">
-        <v>1761.739356115498</v>
-      </c>
-      <c r="H1126" t="n">
-        <v>1753.0778443804</v>
+        <v>1773.817056086561</v>
       </c>
       <c r="I1126" t="n">
-        <v>1743.318234245733</v>
-      </c>
-      <c r="J1126" t="n">
-        <v>58793302310</v>
+        <v>1771.655567491526</v>
       </c>
       <c r="K1126" t="n">
-        <v>61145794679</v>
+        <v>60639155482</v>
       </c>
     </row>
     <row r="1127">
@@ -44366,31 +44354,31 @@
         <v>4500</v>
       </c>
       <c r="E1127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1127" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G1127" t="n">
         <v>1761.739356115498</v>
       </c>
       <c r="H1127" t="n">
-        <v>1733.720824201108</v>
+        <v>1748.663684856989</v>
       </c>
       <c r="I1127" t="n">
-        <v>1740.796072994495</v>
+        <v>1742.937265530643</v>
       </c>
       <c r="J1127" t="n">
-        <v>58755870420</v>
+        <v>58812269481</v>
       </c>
       <c r="K1127" t="n">
-        <v>61540538472</v>
+        <v>61315522970</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>1000.10.3</t>
+          <t>1000.10.2</t>
         </is>
       </c>
       <c r="B1128" t="n">
@@ -44405,31 +44393,31 @@
         <v>4500</v>
       </c>
       <c r="E1128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1128" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G1128" t="n">
-        <v>1748.302363736126</v>
+        <v>1761.739356115498</v>
       </c>
       <c r="H1128" t="n">
-        <v>1764.908007473116</v>
+        <v>1753.0778443804</v>
       </c>
       <c r="I1128" t="n">
-        <v>1760.654491641879</v>
+        <v>1743.318234245733</v>
       </c>
       <c r="J1128" t="n">
-        <v>58893253402</v>
+        <v>58793302310</v>
       </c>
       <c r="K1128" t="n">
-        <v>61164450752</v>
+        <v>61145794679</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>1000.10.3</t>
+          <t>1000.10.2</t>
         </is>
       </c>
       <c r="B1129" t="n">
@@ -44444,31 +44432,31 @@
         <v>4500</v>
       </c>
       <c r="E1129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1129" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G1129" t="n">
-        <v>1748.302363736126</v>
+        <v>1761.739356115498</v>
       </c>
       <c r="H1129" t="n">
-        <v>1745.232279618789</v>
+        <v>1733.720824201108</v>
       </c>
       <c r="I1129" t="n">
-        <v>1749.202199750996</v>
+        <v>1740.796072994495</v>
       </c>
       <c r="J1129" t="n">
-        <v>59297447103</v>
+        <v>58755870420</v>
       </c>
       <c r="K1129" t="n">
-        <v>61614359995</v>
+        <v>61540538472</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>1000.10.3</t>
+          <t>1000.10.2</t>
         </is>
       </c>
       <c r="B1130" t="n">
@@ -44483,31 +44471,25 @@
         <v>4500</v>
       </c>
       <c r="E1130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1130" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G1130" t="n">
-        <v>1748.302363736126</v>
-      </c>
-      <c r="H1130" t="n">
-        <v>1753.412563400108</v>
+        <v>1761.739356115498</v>
       </c>
       <c r="I1130" t="n">
-        <v>1746.964360199898</v>
-      </c>
-      <c r="J1130" t="n">
-        <v>59138365297</v>
+        <v>1737.854667478625</v>
       </c>
       <c r="K1130" t="n">
-        <v>61283413634</v>
+        <v>60993567814</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>1000.10.4</t>
+          <t>1000.10.2</t>
         </is>
       </c>
       <c r="B1131" t="n">
@@ -44522,31 +44504,25 @@
         <v>4500</v>
       </c>
       <c r="E1131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1131" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G1131" t="n">
-        <v>1745.548800328407</v>
-      </c>
-      <c r="H1131" t="n">
-        <v>1724.519140458432</v>
+        <v>1761.739356115498</v>
       </c>
       <c r="I1131" t="n">
-        <v>1730.539238991366</v>
-      </c>
-      <c r="J1131" t="n">
-        <v>59718078278</v>
+        <v>1736.731224875093</v>
       </c>
       <c r="K1131" t="n">
-        <v>62112379253</v>
+        <v>61288617891</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>1000.10.4</t>
+          <t>1000.10.3</t>
         </is>
       </c>
       <c r="B1132" t="n">
@@ -44561,31 +44537,31 @@
         <v>4500</v>
       </c>
       <c r="E1132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1132" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G1132" t="n">
-        <v>1745.548800328407</v>
+        <v>1748.302363736126</v>
       </c>
       <c r="H1132" t="n">
-        <v>1727.349755495702</v>
+        <v>1764.908007473116</v>
       </c>
       <c r="I1132" t="n">
-        <v>1728.751156453611</v>
+        <v>1760.654491641879</v>
       </c>
       <c r="J1132" t="n">
-        <v>59700888210</v>
+        <v>58893253402</v>
       </c>
       <c r="K1132" t="n">
-        <v>61935437391</v>
+        <v>61164450752</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>1000.10.4</t>
+          <t>1000.10.3</t>
         </is>
       </c>
       <c r="B1133" t="n">
@@ -44600,31 +44576,31 @@
         <v>4500</v>
       </c>
       <c r="E1133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1133" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G1133" t="n">
-        <v>1745.548800328407</v>
+        <v>1748.302363736126</v>
       </c>
       <c r="H1133" t="n">
-        <v>1716.732256778813</v>
+        <v>1745.232279618789</v>
       </c>
       <c r="I1133" t="n">
-        <v>1720.205219492753</v>
+        <v>1749.202199750996</v>
       </c>
       <c r="J1133" t="n">
-        <v>59511032983</v>
+        <v>59297447103</v>
       </c>
       <c r="K1133" t="n">
-        <v>62016875497</v>
+        <v>61614359995</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>1000.20.1</t>
+          <t>1000.10.3</t>
         </is>
       </c>
       <c r="B1134" t="n">
@@ -44639,31 +44615,31 @@
         <v>4500</v>
       </c>
       <c r="E1134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1134" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G1134" t="n">
-        <v>3708.541021396037</v>
+        <v>1748.302363736126</v>
       </c>
       <c r="H1134" t="n">
-        <v>3711.484141374198</v>
+        <v>1753.412563400108</v>
       </c>
       <c r="I1134" t="n">
-        <v>3709.684088929843</v>
+        <v>1746.964360199898</v>
       </c>
       <c r="J1134" t="n">
-        <v>54539220721</v>
+        <v>59138365297</v>
       </c>
       <c r="K1134" t="n">
-        <v>57058097271</v>
+        <v>61283413634</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>1000.20.1</t>
+          <t>1000.10.3</t>
         </is>
       </c>
       <c r="B1135" t="n">
@@ -44678,31 +44654,25 @@
         <v>4500</v>
       </c>
       <c r="E1135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1135" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G1135" t="n">
-        <v>3708.541021396037</v>
-      </c>
-      <c r="H1135" t="n">
-        <v>3717.075646092836</v>
+        <v>1748.302363736126</v>
       </c>
       <c r="I1135" t="n">
-        <v>3712.684249728848</v>
-      </c>
-      <c r="J1135" t="n">
-        <v>54746244345</v>
+        <v>1727.103620106004</v>
       </c>
       <c r="K1135" t="n">
-        <v>57502335211</v>
+        <v>61203432562</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>1000.20.1</t>
+          <t>1000.10.3</t>
         </is>
       </c>
       <c r="B1136" t="n">
@@ -44717,31 +44687,25 @@
         <v>4500</v>
       </c>
       <c r="E1136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F1136" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G1136" t="n">
-        <v>3708.541021396037</v>
-      </c>
-      <c r="H1136" t="n">
-        <v>3709.542619220546</v>
+        <v>1748.302363736126</v>
       </c>
       <c r="I1136" t="n">
-        <v>3710.003790441718</v>
-      </c>
-      <c r="J1136" t="n">
-        <v>54542720537</v>
+        <v>1757.041532870469</v>
       </c>
       <c r="K1136" t="n">
-        <v>57084344927</v>
+        <v>61084811192</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>1000.20.2</t>
+          <t>1000.10.4</t>
         </is>
       </c>
       <c r="B1137" t="n">
@@ -44762,25 +44726,25 @@
         <v>100</v>
       </c>
       <c r="G1137" t="n">
-        <v>3768.103517429845</v>
+        <v>1745.548800328407</v>
       </c>
       <c r="H1137" t="n">
-        <v>3718.334914449701</v>
+        <v>1724.519140458432</v>
       </c>
       <c r="I1137" t="n">
-        <v>3707.205779416522</v>
+        <v>1730.539238991366</v>
       </c>
       <c r="J1137" t="n">
-        <v>54522257604</v>
+        <v>59718078278</v>
       </c>
       <c r="K1137" t="n">
-        <v>56748923914</v>
+        <v>62112379253</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>1000.20.2</t>
+          <t>1000.10.4</t>
         </is>
       </c>
       <c r="B1138" t="n">
@@ -44801,25 +44765,25 @@
         <v>200</v>
       </c>
       <c r="G1138" t="n">
-        <v>3768.103517429845</v>
+        <v>1745.548800328407</v>
       </c>
       <c r="H1138" t="n">
-        <v>3712.59434092089</v>
+        <v>1727.349755495702</v>
       </c>
       <c r="I1138" t="n">
-        <v>3688.571250633831</v>
+        <v>1728.751156453611</v>
       </c>
       <c r="J1138" t="n">
-        <v>54713477727</v>
+        <v>59700888210</v>
       </c>
       <c r="K1138" t="n">
-        <v>57558889306</v>
+        <v>61935437391</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>1000.20.2</t>
+          <t>1000.10.4</t>
         </is>
       </c>
       <c r="B1139" t="n">
@@ -44840,25 +44804,25 @@
         <v>300</v>
       </c>
       <c r="G1139" t="n">
-        <v>3768.103517429845</v>
+        <v>1745.548800328407</v>
       </c>
       <c r="H1139" t="n">
-        <v>3730.776752188581</v>
+        <v>1716.732256778813</v>
       </c>
       <c r="I1139" t="n">
-        <v>3725.00272664874</v>
+        <v>1720.205219492753</v>
       </c>
       <c r="J1139" t="n">
-        <v>54778015958</v>
+        <v>59511032983</v>
       </c>
       <c r="K1139" t="n">
-        <v>57374818287</v>
+        <v>62016875497</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>1000.20.3</t>
+          <t>1000.10.4</t>
         </is>
       </c>
       <c r="B1140" t="n">
@@ -44873,31 +44837,25 @@
         <v>4500</v>
       </c>
       <c r="E1140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1140" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G1140" t="n">
-        <v>3734.724211492563</v>
-      </c>
-      <c r="H1140" t="n">
-        <v>3675.718557688236</v>
+        <v>1745.548800328407</v>
       </c>
       <c r="I1140" t="n">
-        <v>3679.378142308556</v>
-      </c>
-      <c r="J1140" t="n">
-        <v>55234934660</v>
+        <v>1729.212291366578</v>
       </c>
       <c r="K1140" t="n">
-        <v>57888578439</v>
+        <v>62343039325</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>1000.20.3</t>
+          <t>1000.10.4</t>
         </is>
       </c>
       <c r="B1141" t="n">
@@ -44912,31 +44870,25 @@
         <v>4500</v>
       </c>
       <c r="E1141" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1141" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G1141" t="n">
-        <v>3734.724211492563</v>
-      </c>
-      <c r="H1141" t="n">
-        <v>3671.040088594132</v>
+        <v>1745.548800328407</v>
       </c>
       <c r="I1141" t="n">
-        <v>3661.716562358774</v>
-      </c>
-      <c r="J1141" t="n">
-        <v>55008199465</v>
+        <v>1725.545009636343</v>
       </c>
       <c r="K1141" t="n">
-        <v>58027715698</v>
+        <v>62305690457</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>1000.20.3</t>
+          <t>1000.20.1</t>
         </is>
       </c>
       <c r="B1142" t="n">
@@ -44951,31 +44903,31 @@
         <v>4500</v>
       </c>
       <c r="E1142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1142" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G1142" t="n">
-        <v>3734.724211492563</v>
+        <v>3708.541021396037</v>
       </c>
       <c r="H1142" t="n">
-        <v>3679.658407988477</v>
+        <v>3711.484141374198</v>
       </c>
       <c r="I1142" t="n">
-        <v>3666.047778478794</v>
+        <v>3709.684088929843</v>
       </c>
       <c r="J1142" t="n">
-        <v>54859740947</v>
+        <v>54539220721</v>
       </c>
       <c r="K1142" t="n">
-        <v>57560856429</v>
+        <v>57058097271</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>1000.20.4</t>
+          <t>1000.20.1</t>
         </is>
       </c>
       <c r="B1143" t="n">
@@ -44990,31 +44942,31 @@
         <v>4500</v>
       </c>
       <c r="E1143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1143" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G1143" t="n">
-        <v>3750.289861862383</v>
+        <v>3708.541021396037</v>
       </c>
       <c r="H1143" t="n">
-        <v>3676.25923851024</v>
+        <v>3717.075646092836</v>
       </c>
       <c r="I1143" t="n">
-        <v>3670.733398781877</v>
+        <v>3712.684249728848</v>
       </c>
       <c r="J1143" t="n">
-        <v>55598291229</v>
+        <v>54746244345</v>
       </c>
       <c r="K1143" t="n">
-        <v>58759408779</v>
+        <v>57502335211</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>1000.20.4</t>
+          <t>1000.20.1</t>
         </is>
       </c>
       <c r="B1144" t="n">
@@ -45029,31 +44981,31 @@
         <v>4500</v>
       </c>
       <c r="E1144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1144" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G1144" t="n">
-        <v>3750.289861862383</v>
+        <v>3708.541021396037</v>
       </c>
       <c r="H1144" t="n">
-        <v>3662.58440372612</v>
+        <v>3709.542619220546</v>
       </c>
       <c r="I1144" t="n">
-        <v>3636.649673462108</v>
+        <v>3710.003790441718</v>
       </c>
       <c r="J1144" t="n">
-        <v>55666781684</v>
+        <v>54542720537</v>
       </c>
       <c r="K1144" t="n">
-        <v>58678113114</v>
+        <v>57084344927</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>1000.20.4</t>
+          <t>1000.20.1</t>
         </is>
       </c>
       <c r="B1145" t="n">
@@ -45068,31 +45020,25 @@
         <v>4500</v>
       </c>
       <c r="E1145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1145" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G1145" t="n">
-        <v>3750.289861862383</v>
-      </c>
-      <c r="H1145" t="n">
-        <v>3640.786747235285</v>
+        <v>3708.541021396037</v>
       </c>
       <c r="I1145" t="n">
-        <v>3626.928613219296</v>
-      </c>
-      <c r="J1145" t="n">
-        <v>55705986427</v>
+        <v>3715.817786494159</v>
       </c>
       <c r="K1145" t="n">
-        <v>58360786268</v>
+        <v>57407086972</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>1000.30.1</t>
+          <t>1000.20.1</t>
         </is>
       </c>
       <c r="B1146" t="n">
@@ -45107,31 +45053,25 @@
         <v>4500</v>
       </c>
       <c r="E1146" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1146" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G1146" t="n">
-        <v>7979.543044930953</v>
-      </c>
-      <c r="H1146" t="n">
-        <v>7909.942853594655</v>
+        <v>3708.541021396037</v>
       </c>
       <c r="I1146" t="n">
-        <v>7903.870424714833</v>
-      </c>
-      <c r="J1146" t="n">
-        <v>75322972139</v>
+        <v>3724.648872747662</v>
       </c>
       <c r="K1146" t="n">
-        <v>80290385520</v>
+        <v>57367898275</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>1000.30.1</t>
+          <t>1000.20.2</t>
         </is>
       </c>
       <c r="B1147" t="n">
@@ -45146,31 +45086,31 @@
         <v>4500</v>
       </c>
       <c r="E1147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1147" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G1147" t="n">
-        <v>7979.543044930953</v>
+        <v>3768.103517429845</v>
       </c>
       <c r="H1147" t="n">
-        <v>7933.369653078021</v>
+        <v>3718.334914449701</v>
       </c>
       <c r="I1147" t="n">
-        <v>7887.053929253325</v>
+        <v>3707.205779416522</v>
       </c>
       <c r="J1147" t="n">
-        <v>75779392870</v>
+        <v>54522257604</v>
       </c>
       <c r="K1147" t="n">
-        <v>80350357454</v>
+        <v>56748923914</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>1000.30.1</t>
+          <t>1000.20.2</t>
         </is>
       </c>
       <c r="B1148" t="n">
@@ -45185,31 +45125,31 @@
         <v>4500</v>
       </c>
       <c r="E1148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1148" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G1148" t="n">
-        <v>7979.543044930953</v>
+        <v>3768.103517429845</v>
       </c>
       <c r="H1148" t="n">
-        <v>7938.674740845327</v>
+        <v>3712.59434092089</v>
       </c>
       <c r="I1148" t="n">
-        <v>7907.193593195034</v>
+        <v>3688.571250633831</v>
       </c>
       <c r="J1148" t="n">
-        <v>75826655517</v>
+        <v>54713477727</v>
       </c>
       <c r="K1148" t="n">
-        <v>80336749536</v>
+        <v>57558889306</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>1000.30.2</t>
+          <t>1000.20.2</t>
         </is>
       </c>
       <c r="B1149" t="n">
@@ -45224,31 +45164,31 @@
         <v>4500</v>
       </c>
       <c r="E1149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1149" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G1149" t="n">
-        <v>7973.009423005142</v>
+        <v>3768.103517429845</v>
       </c>
       <c r="H1149" t="n">
-        <v>7955.478963396214</v>
+        <v>3730.776752188581</v>
       </c>
       <c r="I1149" t="n">
-        <v>7944.300020434308</v>
+        <v>3725.00272664874</v>
       </c>
       <c r="J1149" t="n">
-        <v>75463252430</v>
+        <v>54778015958</v>
       </c>
       <c r="K1149" t="n">
-        <v>79665719147</v>
+        <v>57374818287</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>1000.30.2</t>
+          <t>1000.20.2</t>
         </is>
       </c>
       <c r="B1150" t="n">
@@ -45263,31 +45203,25 @@
         <v>4500</v>
       </c>
       <c r="E1150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1150" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G1150" t="n">
-        <v>7973.009423005142</v>
-      </c>
-      <c r="H1150" t="n">
-        <v>7985.667796737807</v>
+        <v>3768.103517429845</v>
       </c>
       <c r="I1150" t="n">
-        <v>7950.033926181859</v>
-      </c>
-      <c r="J1150" t="n">
-        <v>75499709671</v>
+        <v>3731.317629012444</v>
       </c>
       <c r="K1150" t="n">
-        <v>79559486593</v>
+        <v>57923996919</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>1000.30.2</t>
+          <t>1000.20.2</t>
         </is>
       </c>
       <c r="B1151" t="n">
@@ -45302,31 +45236,25 @@
         <v>4500</v>
       </c>
       <c r="E1151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F1151" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G1151" t="n">
-        <v>7973.009423005142</v>
-      </c>
-      <c r="H1151" t="n">
-        <v>7971.863557246797</v>
+        <v>3768.103517429845</v>
       </c>
       <c r="I1151" t="n">
-        <v>7945.713457379617</v>
-      </c>
-      <c r="J1151" t="n">
-        <v>75291910014</v>
+        <v>3698.256619021398</v>
       </c>
       <c r="K1151" t="n">
-        <v>79646776106</v>
+        <v>57292622262</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>1000.30.3</t>
+          <t>1000.20.3</t>
         </is>
       </c>
       <c r="B1152" t="n">
@@ -45347,25 +45275,25 @@
         <v>100</v>
       </c>
       <c r="G1152" t="n">
-        <v>7977.814850915422</v>
+        <v>3734.724211492563</v>
       </c>
       <c r="H1152" t="n">
-        <v>7912.800374705674</v>
+        <v>3675.718557688236</v>
       </c>
       <c r="I1152" t="n">
-        <v>7920.722535902631</v>
+        <v>3679.378142308556</v>
       </c>
       <c r="J1152" t="n">
-        <v>75526679782</v>
+        <v>55234934660</v>
       </c>
       <c r="K1152" t="n">
-        <v>79864223403</v>
+        <v>57888578439</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>1000.30.3</t>
+          <t>1000.20.3</t>
         </is>
       </c>
       <c r="B1153" t="n">
@@ -45386,25 +45314,25 @@
         <v>200</v>
       </c>
       <c r="G1153" t="n">
-        <v>7977.814850915422</v>
+        <v>3734.724211492563</v>
       </c>
       <c r="H1153" t="n">
-        <v>7920.286934325561</v>
+        <v>3671.040088594132</v>
       </c>
       <c r="I1153" t="n">
-        <v>7876.350396623391</v>
+        <v>3661.716562358774</v>
       </c>
       <c r="J1153" t="n">
-        <v>75239934410</v>
+        <v>55008199465</v>
       </c>
       <c r="K1153" t="n">
-        <v>79854507057</v>
+        <v>58027715698</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>1000.30.3</t>
+          <t>1000.20.3</t>
         </is>
       </c>
       <c r="B1154" t="n">
@@ -45425,25 +45353,25 @@
         <v>300</v>
       </c>
       <c r="G1154" t="n">
-        <v>7977.814850915422</v>
+        <v>3734.724211492563</v>
       </c>
       <c r="H1154" t="n">
-        <v>7913.559085252405</v>
+        <v>3679.658407988477</v>
       </c>
       <c r="I1154" t="n">
-        <v>7860.33109598247</v>
+        <v>3666.047778478794</v>
       </c>
       <c r="J1154" t="n">
-        <v>75154106633</v>
+        <v>54859740947</v>
       </c>
       <c r="K1154" t="n">
-        <v>79559590331</v>
+        <v>57560856429</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>1000.30.4</t>
+          <t>1000.20.3</t>
         </is>
       </c>
       <c r="B1155" t="n">
@@ -45458,31 +45386,25 @@
         <v>4500</v>
       </c>
       <c r="E1155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1155" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G1155" t="n">
-        <v>7964.046250435393</v>
-      </c>
-      <c r="H1155" t="n">
-        <v>7954.622756722229</v>
+        <v>3734.724211492563</v>
       </c>
       <c r="I1155" t="n">
-        <v>7937.350316798198</v>
-      </c>
-      <c r="J1155" t="n">
-        <v>76298686901</v>
+        <v>3671.922246025872</v>
       </c>
       <c r="K1155" t="n">
-        <v>80345994552</v>
+        <v>57868215020</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>1000.30.4</t>
+          <t>1000.20.3</t>
         </is>
       </c>
       <c r="B1156" t="n">
@@ -45497,31 +45419,25 @@
         <v>4500</v>
       </c>
       <c r="E1156" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1156" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G1156" t="n">
-        <v>7964.046250435393</v>
-      </c>
-      <c r="H1156" t="n">
-        <v>7944.878378597256</v>
+        <v>3734.724211492563</v>
       </c>
       <c r="I1156" t="n">
-        <v>7945.437917149456</v>
-      </c>
-      <c r="J1156" t="n">
-        <v>76143958723</v>
+        <v>3692.032536338156</v>
       </c>
       <c r="K1156" t="n">
-        <v>80072300346</v>
+        <v>57612007483</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>1000.30.4</t>
+          <t>1000.20.4</t>
         </is>
       </c>
       <c r="B1157" t="n">
@@ -45536,31 +45452,31 @@
         <v>4500</v>
       </c>
       <c r="E1157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1157" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G1157" t="n">
-        <v>7964.046250435393</v>
+        <v>3750.289861862383</v>
       </c>
       <c r="H1157" t="n">
-        <v>7908.149940826446</v>
+        <v>3676.25923851024</v>
       </c>
       <c r="I1157" t="n">
-        <v>7924.585067946708</v>
+        <v>3670.733398781877</v>
       </c>
       <c r="J1157" t="n">
-        <v>76310818841</v>
+        <v>55598291229</v>
       </c>
       <c r="K1157" t="n">
-        <v>80329220533</v>
+        <v>58759408779</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>1000.40.1</t>
+          <t>1000.20.4</t>
         </is>
       </c>
       <c r="B1158" t="n">
@@ -45575,31 +45491,31 @@
         <v>4500</v>
       </c>
       <c r="E1158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1158" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G1158" t="n">
-        <v>14005.02994874948</v>
+        <v>3750.289861862383</v>
       </c>
       <c r="H1158" t="n">
-        <v>13804.65911026816</v>
+        <v>3662.58440372612</v>
       </c>
       <c r="I1158" t="n">
-        <v>13727.06070999957</v>
+        <v>3636.649673462108</v>
       </c>
       <c r="J1158" t="n">
-        <v>85252367167</v>
+        <v>55666781684</v>
       </c>
       <c r="K1158" t="n">
-        <v>87948448001</v>
+        <v>58678113114</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>1000.40.1</t>
+          <t>1000.20.4</t>
         </is>
       </c>
       <c r="B1159" t="n">
@@ -45614,31 +45530,31 @@
         <v>4500</v>
       </c>
       <c r="E1159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1159" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G1159" t="n">
-        <v>14005.02994874948</v>
+        <v>3750.289861862383</v>
       </c>
       <c r="H1159" t="n">
-        <v>13703.5761313689</v>
+        <v>3640.786747235285</v>
       </c>
       <c r="I1159" t="n">
-        <v>13678.77539809002</v>
+        <v>3626.928613219296</v>
       </c>
       <c r="J1159" t="n">
-        <v>85000059396</v>
+        <v>55705986427</v>
       </c>
       <c r="K1159" t="n">
-        <v>88387691033</v>
+        <v>58360786268</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>1000.40.1</t>
+          <t>1000.20.4</t>
         </is>
       </c>
       <c r="B1160" t="n">
@@ -45653,31 +45569,25 @@
         <v>4500</v>
       </c>
       <c r="E1160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1160" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G1160" t="n">
-        <v>14005.02994874948</v>
-      </c>
-      <c r="H1160" t="n">
-        <v>13829.70485039924</v>
+        <v>3750.289861862383</v>
       </c>
       <c r="I1160" t="n">
-        <v>13707.46434839891</v>
-      </c>
-      <c r="J1160" t="n">
-        <v>84913861591</v>
+        <v>3649.085715187551</v>
       </c>
       <c r="K1160" t="n">
-        <v>88130654686</v>
+        <v>58460871742</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>1000.40.2</t>
+          <t>1000.20.4</t>
         </is>
       </c>
       <c r="B1161" t="n">
@@ -45692,31 +45602,25 @@
         <v>4500</v>
       </c>
       <c r="E1161" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1161" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G1161" t="n">
-        <v>14118.04105210099</v>
-      </c>
-      <c r="H1161" t="n">
-        <v>13953.57733794516</v>
+        <v>3750.289861862383</v>
       </c>
       <c r="I1161" t="n">
-        <v>13931.39017551439</v>
-      </c>
-      <c r="J1161" t="n">
-        <v>84476830074</v>
+        <v>3653.587321404143</v>
       </c>
       <c r="K1161" t="n">
-        <v>88463191445</v>
+        <v>58573086462</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>1000.40.2</t>
+          <t>1000.30.1</t>
         </is>
       </c>
       <c r="B1162" t="n">
@@ -45731,31 +45635,31 @@
         <v>4500</v>
       </c>
       <c r="E1162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1162" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G1162" t="n">
-        <v>14118.04105210099</v>
+        <v>7979.543044930953</v>
       </c>
       <c r="H1162" t="n">
-        <v>13879.86269944144</v>
+        <v>7909.942853594655</v>
       </c>
       <c r="I1162" t="n">
-        <v>13850.72930858321</v>
+        <v>7903.870424714833</v>
       </c>
       <c r="J1162" t="n">
-        <v>84567750703</v>
+        <v>75322972139</v>
       </c>
       <c r="K1162" t="n">
-        <v>88374159109</v>
+        <v>80290385520</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>1000.40.2</t>
+          <t>1000.30.1</t>
         </is>
       </c>
       <c r="B1163" t="n">
@@ -45770,31 +45674,31 @@
         <v>4500</v>
       </c>
       <c r="E1163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1163" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G1163" t="n">
-        <v>14118.04105210099</v>
+        <v>7979.543044930953</v>
       </c>
       <c r="H1163" t="n">
-        <v>13960.02681644472</v>
+        <v>7933.369653078021</v>
       </c>
       <c r="I1163" t="n">
-        <v>13917.82365179558</v>
+        <v>7887.053929253325</v>
       </c>
       <c r="J1163" t="n">
-        <v>84895471386</v>
+        <v>75779392870</v>
       </c>
       <c r="K1163" t="n">
-        <v>88267450156</v>
+        <v>80350357454</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>1000.40.3</t>
+          <t>1000.30.1</t>
         </is>
       </c>
       <c r="B1164" t="n">
@@ -45809,31 +45713,31 @@
         <v>4500</v>
       </c>
       <c r="E1164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1164" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G1164" t="n">
-        <v>14052.70747046845</v>
+        <v>7979.543044930953</v>
       </c>
       <c r="H1164" t="n">
-        <v>13928.43424030587</v>
+        <v>7938.674740845327</v>
       </c>
       <c r="I1164" t="n">
-        <v>13866.49181471369</v>
+        <v>7907.193593195034</v>
       </c>
       <c r="J1164" t="n">
-        <v>84955360440</v>
+        <v>75826655517</v>
       </c>
       <c r="K1164" t="n">
-        <v>88491758334</v>
+        <v>80336749536</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>1000.40.3</t>
+          <t>1000.30.1</t>
         </is>
       </c>
       <c r="B1165" t="n">
@@ -45848,31 +45752,25 @@
         <v>4500</v>
       </c>
       <c r="E1165" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1165" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G1165" t="n">
-        <v>14052.70747046845</v>
-      </c>
-      <c r="H1165" t="n">
-        <v>14025.13225262927</v>
+        <v>7979.543044930953</v>
       </c>
       <c r="I1165" t="n">
-        <v>13992.15523571734</v>
-      </c>
-      <c r="J1165" t="n">
-        <v>84845024911</v>
+        <v>7928.849627264417</v>
       </c>
       <c r="K1165" t="n">
-        <v>88258794676</v>
+        <v>80058172429</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>1000.40.3</t>
+          <t>1000.30.1</t>
         </is>
       </c>
       <c r="B1166" t="n">
@@ -45887,31 +45785,25 @@
         <v>4500</v>
       </c>
       <c r="E1166" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F1166" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G1166" t="n">
-        <v>14052.70747046845</v>
-      </c>
-      <c r="H1166" t="n">
-        <v>13988.34944155203</v>
+        <v>7979.543044930953</v>
       </c>
       <c r="I1166" t="n">
-        <v>13922.58586497711</v>
-      </c>
-      <c r="J1166" t="n">
-        <v>85041302241</v>
+        <v>7918.811182482041</v>
       </c>
       <c r="K1166" t="n">
-        <v>88291746606</v>
+        <v>80136357169</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>1000.40.4</t>
+          <t>1000.30.2</t>
         </is>
       </c>
       <c r="B1167" t="n">
@@ -45932,25 +45824,25 @@
         <v>100</v>
       </c>
       <c r="G1167" t="n">
-        <v>14047.58679159633</v>
+        <v>7973.009423005142</v>
       </c>
       <c r="H1167" t="n">
-        <v>13855.13481452877</v>
+        <v>7955.478963396214</v>
       </c>
       <c r="I1167" t="n">
-        <v>13769.51168139956</v>
+        <v>7944.300020434308</v>
       </c>
       <c r="J1167" t="n">
-        <v>84108180671</v>
+        <v>75463252430</v>
       </c>
       <c r="K1167" t="n">
-        <v>88169613935</v>
+        <v>79665719147</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>1000.40.4</t>
+          <t>1000.30.2</t>
         </is>
       </c>
       <c r="B1168" t="n">
@@ -45971,25 +45863,25 @@
         <v>200</v>
       </c>
       <c r="G1168" t="n">
-        <v>14047.58679159633</v>
+        <v>7973.009423005142</v>
       </c>
       <c r="H1168" t="n">
-        <v>13808.05311567009</v>
+        <v>7985.667796737807</v>
       </c>
       <c r="I1168" t="n">
-        <v>13792.0484138216</v>
+        <v>7950.033926181859</v>
       </c>
       <c r="J1168" t="n">
-        <v>83932164076</v>
+        <v>75499709671</v>
       </c>
       <c r="K1168" t="n">
-        <v>87849710144</v>
+        <v>79559486593</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>1000.40.4</t>
+          <t>1000.30.2</t>
         </is>
       </c>
       <c r="B1169" t="n">
@@ -46010,19 +45902,1183 @@
         <v>300</v>
       </c>
       <c r="G1169" t="n">
+        <v>7973.009423005142</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>7971.863557246797</v>
+      </c>
+      <c r="I1169" t="n">
+        <v>7945.713457379617</v>
+      </c>
+      <c r="J1169" t="n">
+        <v>75291910014</v>
+      </c>
+      <c r="K1169" t="n">
+        <v>79646776106</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>1000.30.2</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1170" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>7973.009423005142</v>
+      </c>
+      <c r="I1170" t="n">
+        <v>7959.459092132034</v>
+      </c>
+      <c r="K1170" t="n">
+        <v>79191579668</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>1000.30.2</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1171" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>7973.009423005142</v>
+      </c>
+      <c r="I1171" t="n">
+        <v>7970.03120460759</v>
+      </c>
+      <c r="K1171" t="n">
+        <v>80012508520</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>1000.30.3</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1172" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>7977.814850915422</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>7912.800374705674</v>
+      </c>
+      <c r="I1172" t="n">
+        <v>7920.722535902631</v>
+      </c>
+      <c r="J1172" t="n">
+        <v>75526679782</v>
+      </c>
+      <c r="K1172" t="n">
+        <v>79864223403</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>1000.30.3</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1173" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>7977.814850915422</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>7920.286934325561</v>
+      </c>
+      <c r="I1173" t="n">
+        <v>7876.350396623391</v>
+      </c>
+      <c r="J1173" t="n">
+        <v>75239934410</v>
+      </c>
+      <c r="K1173" t="n">
+        <v>79854507057</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>1000.30.3</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1174" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1174" t="n">
+        <v>7977.814850915422</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>7913.559085252405</v>
+      </c>
+      <c r="I1174" t="n">
+        <v>7860.33109598247</v>
+      </c>
+      <c r="J1174" t="n">
+        <v>75154106633</v>
+      </c>
+      <c r="K1174" t="n">
+        <v>79559590331</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>1000.30.3</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1175" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1175" t="n">
+        <v>7977.814850915422</v>
+      </c>
+      <c r="I1175" t="n">
+        <v>7920.365306495831</v>
+      </c>
+      <c r="K1175" t="n">
+        <v>79839038862</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>1000.30.3</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1176" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>7977.814850915422</v>
+      </c>
+      <c r="I1176" t="n">
+        <v>7864.197629346444</v>
+      </c>
+      <c r="K1176" t="n">
+        <v>79809132821</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>1000.30.4</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1177" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>7964.046250435393</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>7954.622756722229</v>
+      </c>
+      <c r="I1177" t="n">
+        <v>7937.350316798198</v>
+      </c>
+      <c r="J1177" t="n">
+        <v>76298686901</v>
+      </c>
+      <c r="K1177" t="n">
+        <v>80345994552</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>1000.30.4</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1178" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>7964.046250435393</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>7944.878378597256</v>
+      </c>
+      <c r="I1178" t="n">
+        <v>7945.437917149456</v>
+      </c>
+      <c r="J1178" t="n">
+        <v>76143958723</v>
+      </c>
+      <c r="K1178" t="n">
+        <v>80072300346</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>1000.30.4</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1179" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>7964.046250435393</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>7908.149940826446</v>
+      </c>
+      <c r="I1179" t="n">
+        <v>7924.585067946708</v>
+      </c>
+      <c r="J1179" t="n">
+        <v>76310818841</v>
+      </c>
+      <c r="K1179" t="n">
+        <v>80329220533</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>1000.30.4</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1180" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>7964.046250435393</v>
+      </c>
+      <c r="I1180" t="n">
+        <v>7929.577010942594</v>
+      </c>
+      <c r="K1180" t="n">
+        <v>79863930995</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>1000.30.4</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1181" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>7964.046250435393</v>
+      </c>
+      <c r="I1181" t="n">
+        <v>7907.056895020358</v>
+      </c>
+      <c r="K1181" t="n">
+        <v>80221553843</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>1000.40.1</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1182" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>14005.02994874948</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>13804.65911026816</v>
+      </c>
+      <c r="I1182" t="n">
+        <v>13727.06070999957</v>
+      </c>
+      <c r="J1182" t="n">
+        <v>85252367167</v>
+      </c>
+      <c r="K1182" t="n">
+        <v>87948448001</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>1000.40.1</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1183" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>14005.02994874948</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>13703.5761313689</v>
+      </c>
+      <c r="I1183" t="n">
+        <v>13678.77539809002</v>
+      </c>
+      <c r="J1183" t="n">
+        <v>85000059396</v>
+      </c>
+      <c r="K1183" t="n">
+        <v>88387691033</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>1000.40.1</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1184" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>14005.02994874948</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>13829.70485039924</v>
+      </c>
+      <c r="I1184" t="n">
+        <v>13707.46434839891</v>
+      </c>
+      <c r="J1184" t="n">
+        <v>84913861591</v>
+      </c>
+      <c r="K1184" t="n">
+        <v>88130654686</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>1000.40.1</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1185" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>14005.02994874948</v>
+      </c>
+      <c r="I1185" t="n">
+        <v>13740.21554885748</v>
+      </c>
+      <c r="K1185" t="n">
+        <v>88297144687</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>1000.40.1</t>
+        </is>
+      </c>
+      <c r="B1186" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1186" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>14005.02994874948</v>
+      </c>
+      <c r="I1186" t="n">
+        <v>13666.85921821061</v>
+      </c>
+      <c r="K1186" t="n">
+        <v>88392609632</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>1000.40.2</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1187" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>14118.04105210099</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>13953.57733794516</v>
+      </c>
+      <c r="I1187" t="n">
+        <v>13931.39017551439</v>
+      </c>
+      <c r="J1187" t="n">
+        <v>84476830074</v>
+      </c>
+      <c r="K1187" t="n">
+        <v>88463191445</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>1000.40.2</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1188" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>14118.04105210099</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>13879.86269944144</v>
+      </c>
+      <c r="I1188" t="n">
+        <v>13850.72930858321</v>
+      </c>
+      <c r="J1188" t="n">
+        <v>84567750703</v>
+      </c>
+      <c r="K1188" t="n">
+        <v>88374159109</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>1000.40.2</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1189" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>14118.04105210099</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>13960.02681644472</v>
+      </c>
+      <c r="I1189" t="n">
+        <v>13917.82365179558</v>
+      </c>
+      <c r="J1189" t="n">
+        <v>84895471386</v>
+      </c>
+      <c r="K1189" t="n">
+        <v>88267450156</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>1000.40.2</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1190" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>14118.04105210099</v>
+      </c>
+      <c r="I1190" t="n">
+        <v>13860.35154425662</v>
+      </c>
+      <c r="K1190" t="n">
+        <v>88312094525</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>1000.40.2</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1191" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>14118.04105210099</v>
+      </c>
+      <c r="I1191" t="n">
+        <v>13816.65492916855</v>
+      </c>
+      <c r="K1191" t="n">
+        <v>88256861778</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>1000.40.3</t>
+        </is>
+      </c>
+      <c r="B1192" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1192" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>14052.70747046845</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>13928.43424030587</v>
+      </c>
+      <c r="I1192" t="n">
+        <v>13866.49181471369</v>
+      </c>
+      <c r="J1192" t="n">
+        <v>84955360440</v>
+      </c>
+      <c r="K1192" t="n">
+        <v>88491758334</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>1000.40.3</t>
+        </is>
+      </c>
+      <c r="B1193" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1193" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>14052.70747046845</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>14025.13225262927</v>
+      </c>
+      <c r="I1193" t="n">
+        <v>13992.15523571734</v>
+      </c>
+      <c r="J1193" t="n">
+        <v>84845024911</v>
+      </c>
+      <c r="K1193" t="n">
+        <v>88258794676</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>1000.40.3</t>
+        </is>
+      </c>
+      <c r="B1194" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1194" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>14052.70747046845</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>13988.34944155203</v>
+      </c>
+      <c r="I1194" t="n">
+        <v>13922.58586497711</v>
+      </c>
+      <c r="J1194" t="n">
+        <v>85041302241</v>
+      </c>
+      <c r="K1194" t="n">
+        <v>88291746606</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>1000.40.3</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1195" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1195" t="n">
+        <v>14052.70747046845</v>
+      </c>
+      <c r="I1195" t="n">
+        <v>13985.74834269132</v>
+      </c>
+      <c r="K1195" t="n">
+        <v>88070207994</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>1000.40.3</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1196" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1196" t="n">
+        <v>14052.70747046845</v>
+      </c>
+      <c r="I1196" t="n">
+        <v>13920.36568946934</v>
+      </c>
+      <c r="K1196" t="n">
+        <v>88382124558</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>1000.40.4</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1197" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1197" t="n">
         <v>14047.58679159633</v>
       </c>
-      <c r="H1169" t="n">
+      <c r="H1197" t="n">
+        <v>13855.13481452877</v>
+      </c>
+      <c r="I1197" t="n">
+        <v>13769.51168139956</v>
+      </c>
+      <c r="J1197" t="n">
+        <v>84108180671</v>
+      </c>
+      <c r="K1197" t="n">
+        <v>88169613935</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>1000.40.4</t>
+        </is>
+      </c>
+      <c r="B1198" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1198" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1198" t="n">
+        <v>14047.58679159633</v>
+      </c>
+      <c r="H1198" t="n">
+        <v>13808.05311567009</v>
+      </c>
+      <c r="I1198" t="n">
+        <v>13792.0484138216</v>
+      </c>
+      <c r="J1198" t="n">
+        <v>83932164076</v>
+      </c>
+      <c r="K1198" t="n">
+        <v>87849710144</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>1000.40.4</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1199" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>14047.58679159633</v>
+      </c>
+      <c r="H1199" t="n">
         <v>13788.06577326823</v>
       </c>
-      <c r="I1169" t="n">
+      <c r="I1199" t="n">
         <v>13833.52844773018</v>
       </c>
-      <c r="J1169" t="n">
+      <c r="J1199" t="n">
         <v>84099856887</v>
       </c>
-      <c r="K1169" t="n">
+      <c r="K1199" t="n">
         <v>88168171393</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>1000.40.4</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1200" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1200" t="n">
+        <v>14047.58679159633</v>
+      </c>
+      <c r="I1200" t="n">
+        <v>13774.94086040058</v>
+      </c>
+      <c r="K1200" t="n">
+        <v>87919633198</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>1000.40.4</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>held-out</t>
+        </is>
+      </c>
+      <c r="D1201" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>14047.58679159633</v>
+      </c>
+      <c r="I1201" t="n">
+        <v>13832.13975302853</v>
+      </c>
+      <c r="K1201" t="n">
+        <v>87930082279</v>
       </c>
     </row>
   </sheetData>
